--- a/HUD_field_reqs_by_project_type_by_field.xlsx
+++ b/HUD_field_reqs_by_project_type_by_field.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -1155,20 +1155,20 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit
-1: Emergency Shelter – Night-by-Night
-2: Transitional Housing
-3: PH – Permanent Supportive Housing (disability required for entry)
-4: Street Outreach
-5: RETIRED
-6: Services Only
-7: Other
-8: Safe Haven
-9: PH – Housing Only
-10: PH – Housing with Services (no disability required for entry)
-11: Day Shelter
-12: Homelessness Prevention
-13: PH – Rapid Re-Housing
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+4: Street Outreach;
+5: RETIRED;
+6: Services Only;
+7: Other;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services (no disability required for entry);
+11: Day Shelter;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing;
 14: Coordinated Entry</t>
         </is>
       </c>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1: RRH: Services Only
+          <t>1: RRH: Services Only;
 2: RRH: Housing with or without services</t>
         </is>
       </c>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -1475,8 +1475,8 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1: Site-based – single site
-2: Site-based – clustered/multiple sites
+          <t>1: Site-based – single site;
+2: Site-based – clustered/multiple sites;
 3: Tenant-based – scattered site</t>
         </is>
       </c>
@@ -1554,8 +1554,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1: DV: Survivors of Domestic Violence
-3: HIV: Persons with HIV/AIDS
+          <t>1: DV: Survivors of Domestic Violence;
+3: HIV: Persons with HIV/AIDS;
 4: NA: Not applicable</t>
         </is>
       </c>
@@ -1633,8 +1633,8 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
+          <t>0: No;
+1: Yes;
 2: NA – non-HOPWA Funded Project</t>
         </is>
       </c>
@@ -2139,8 +2139,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1: Urban
-2: Suburban
+          <t>1: Urban;
+2: Suburban;
 3: Rural</t>
         </is>
       </c>
@@ -2206,55 +2206,55 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1: HUD: CoC – Homelessness Prevention (High Performing Comm. Only)
-2: HUD: CoC – Permanent Supportive Housing
-3: HUD: CoC – Rapid Re-Housing
-4: HUD: CoC – Supportive Services Only
-5: HUD: CoC – Transitional Housing
-6: HUD: CoC – Safe Haven
-7: HUD: CoC – Single Room Occupancy (SRO)
-43: HUD: CoC – Youth Homeless Demonstration Program (YHDP)
-44: HUD: CoC – Joint Component TH/RRH
-56: HUD: CoC Builds
-8: HUD: ESG – Emergency Shelter (operating and/or essential services)
-9: HUD: ESG – Homelessness Prevention
-10: HUD: ESG – Rapid Re-Housing
-11: HUD: ESG – Street Outreach
-47: HUD: ESG-CV [Retired]
-53: HUD: ESG-RUSH
-54: HUD: Unsheltered Special NOFO
-55: HUD: Rural Special NOFO
-35: HUD: Pay for Success
-13: HUD: HOPWA – Hotel/Motel Vouchers
-14: HUD: HOPWA – Housing Information
-15: HUD: HOPWA – Permanent Housing (facility based or TBRA)
-16: HUD: HOPWA – Permanent Housing Placement
-17: HUD: HOPWA – Short-Term Rent, Mortgage, Utility assistance
-18: HUD: HOPWA – Short-Term Supportive Facility
-19: HUD: HOPWA – Transitional Housing (facility based or TBRA)
-48: HUD: HOPWA-CV [Retired]
-36: HUD: Public and Indian Housing (PIH) Programs
-20: HUD: HUD/VASH
-52: HUD: PIH (Emergency Housing Voucher)
-50: HUD: HOME
-51: HUD: HOME (ARP)
-21: HHS: PATH – Street Outreach &amp; Supportive Services Only
-22: HHS: RHY – Basic Center Program (prevention and shelter)
-23: HHS: RHY – Maternity Group Home for Pregnant and Parenting Youth
-24: HHS: RHY – Transitional Living Program
-25: HHS: RHY – Street Outreach Project
-26: HHS: RHY – Demonstration Project
-27: VA: CRS Contract Residential Services
-37: VA: Grant Per Diem – Bridge Housing
-38: VA: Grant Per Diem – Low Demand
-39: VA: Grant Per Diem – Hospital to Housing
-40: VA: Grant Per Diem – Clinical Treatment
-41: VA: Grant Per Diem – Service Intensive Transitional Housing
-42: VA: Grant Per Diem – Transition in Place
-45: VA: Grant Per Diem – Case Management/Housing Retention
-30: VA: Community Contract Safe Haven Program
-33: VA: Supportive Services for Veteran Families
-34: N/A
+          <t>1: HUD: CoC – Homelessness Prevention (High Performing Comm. Only);
+2: HUD: CoC – Permanent Supportive Housing;
+3: HUD: CoC – Rapid Re-Housing;
+4: HUD: CoC – Supportive Services Only;
+5: HUD: CoC – Transitional Housing;
+6: HUD: CoC – Safe Haven;
+7: HUD: CoC – Single Room Occupancy (SRO);
+43: HUD: CoC – Youth Homeless Demonstration Program (YHDP);
+44: HUD: CoC – Joint Component TH/RRH;
+56: HUD: CoC Builds;
+8: HUD: ESG – Emergency Shelter (operating and/or essential services);
+9: HUD: ESG – Homelessness Prevention;
+10: HUD: ESG – Rapid Re-Housing;
+11: HUD: ESG – Street Outreach;
+47: HUD: ESG-CV [Retired];
+53: HUD: ESG-RUSH;
+54: HUD: Unsheltered Special NOFO;
+55: HUD: Rural Special NOFO;
+35: HUD: Pay for Success;
+13: HUD: HOPWA – Hotel/Motel Vouchers;
+14: HUD: HOPWA – Housing Information;
+15: HUD: HOPWA – Permanent Housing (facility based or TBRA);
+16: HUD: HOPWA – Permanent Housing Placement;
+17: HUD: HOPWA – Short-Term Rent, Mortgage, Utility assistance;
+18: HUD: HOPWA – Short-Term Supportive Facility;
+19: HUD: HOPWA – Transitional Housing (facility based or TBRA);
+48: HUD: HOPWA-CV [Retired];
+36: HUD: Public and Indian Housing (PIH) Programs;
+20: HUD: HUD/VASH;
+52: HUD: PIH (Emergency Housing Voucher);
+50: HUD: HOME;
+51: HUD: HOME (ARP);
+21: HHS: PATH – Street Outreach &amp; Supportive Services Only;
+22: HHS: RHY – Basic Center Program (prevention and shelter);
+23: HHS: RHY – Maternity Group Home for Pregnant and Parenting Youth;
+24: HHS: RHY – Transitional Living Program;
+25: HHS: RHY – Street Outreach Project;
+26: HHS: RHY – Demonstration Project;
+27: VA: CRS Contract Residential Services;
+37: VA: Grant Per Diem – Bridge Housing;
+38: VA: Grant Per Diem – Low Demand;
+39: VA: Grant Per Diem – Hospital to Housing;
+40: VA: Grant Per Diem – Clinical Treatment;
+41: VA: Grant Per Diem – Service Intensive Transitional Housing;
+42: VA: Grant Per Diem – Transition in Place;
+45: VA: Grant Per Diem – Case Management/Housing Retention;
+30: VA: Community Contract Safe Haven Program;
+33: VA: Supportive Services for Veteran Families;
+34: N/A;
 46: Local or Other Funding Source (Please Specify)</t>
         </is>
       </c>
@@ -2635,7 +2635,14 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2708,7 +2715,14 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2781,7 +2795,14 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2843,8 +2864,8 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1: Households without children
-3: Households with at least one adult and one child
+          <t>1: Households without children;
+3: Households with at least one adult and one child;
 4: Households with only children</t>
         </is>
       </c>
@@ -2860,7 +2881,14 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2922,8 +2950,8 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>1: Facility-based beds
-2: Voucher beds
+          <t>1: Facility-based beds;
+2: Voucher beds;
 3: Other beds</t>
         </is>
       </c>
@@ -2939,7 +2967,14 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3001,8 +3036,8 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1: Year-round
-2: Seasonal
+          <t>1: Year-round;
+2: Seasonal;
 3: Overflow</t>
         </is>
       </c>
@@ -3018,7 +3053,14 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3091,7 +3133,14 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3164,7 +3213,14 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3237,7 +3293,14 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -3310,7 +3373,14 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3383,7 +3453,14 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3456,7 +3533,14 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3529,7 +3613,14 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3602,7 +3693,14 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3675,7 +3773,14 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing 8: Safe Haven 9: PH – Housing Only 10: PH – Housing with Services 13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing;
+8: Safe Haven;
+9: PH – Housing Only;
+10: PH – Housing with Services;
+13: PH – Rapid Re-Housing (subtype 2: RRH: Housing with or without services)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3737,8 +3842,8 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>0: Not Participating
-1: HMIS Participating
+          <t>0: Not Participating;
+1: HMIS Participating;
 2: Comparable Database Participating</t>
         </is>
       </c>
@@ -3962,7 +4067,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -4040,9 +4145,9 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>1: Homelessness Prevention Assessment, Screening, and/or Referral
-2: Shelter Assessment, Screening, and/or Referral
-3: Housing Assessment, Screening, and/or Referral
+          <t>1: Homelessness Prevention Assessment, Screening, and/or Referral;
+2: Shelter Assessment, Screening, and/or Referral;
+3: Housing Assessment, Screening, and/or Referral;
 4: Direct Services (search and/or placement support)</t>
         </is>
       </c>
@@ -4120,7 +4225,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -4668,10 +4773,10 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>1: Full name reported
-2: Partial, street name, or code name reported
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Full name reported;
+2: Partial, street name, or code name reported;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -4838,10 +4943,10 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>1: Full SSN reported
-2: Approximate or partial SSN reported
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Full SSN reported;
+2: Approximate or partial SSN reported;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -5008,10 +5113,10 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>1: Full DOB reported
-2: Approximate or partial DOB reported
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Full DOB reported;
+2: Approximate or partial DOB reported;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -5097,15 +5202,15 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>1: American Indian, Alaska Native, or Indigenous
-2: Asian or Asian American
-3: Black, African American, or African
-6: Hispanic/Latina/o
-7: Middle Eastern or North African
-4: Native Hawaiian or Pacific Islander
-5: White
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: American Indian, Alaska Native, or Indigenous;
+2: Asian or Asian American;
+3: Black, African American, or African;
+6: Hispanic/Latina/o;
+7: Middle Eastern or North African;
+4: Native Hawaiian or Pacific Islander;
+5: White;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -5272,10 +5377,10 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -5361,10 +5466,10 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -5855,10 +5960,10 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>1: Self (Head of Household)
-2: Head of Household’s child
-3: Head of Household’s spouse or partner
-4: Head of Household’s other relation member (other relation to Head of Household)
+          <t>1: Self (Head of Household);
+2: Head of Household’s child;
+3: Head of Household’s spouse or partner;
+4: Head of Household’s other relation member (other relation to Head of Household);
 5: Other: non-relation member</t>
         </is>
       </c>
@@ -6031,12 +6136,19 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>All Programs – All Permanent Housing Components Pay for Success – All component types VA: Grant Per Diem – Case Management/Housing Retention</t>
+          <t>All Programs – All Permanent Housing Components;
+Pay for Success – All component types;
+VA: Grant Per Diem – Case Management/Housing Retention</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>3: PH – Permanent Supportive Housing 6: Services Only (VA: GPD CM/HR ONLY) 7: Other (Pay for Success ONLY) 9: PH – Housing Only 10: PH – Housing with Services (no disability required for entry) 13: PH – Rapid Re-Housing</t>
+          <t>3: PH – Permanent Supportive Housing;
+6: Services Only (VA: GPD CM/HR ONLY);
+7: Other (Pay for Success ONLY);
+9: PH – Housing Only;
+10: PH – Housing with Services (no disability required for entry);
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -6117,7 +6229,10 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 4: Street Outreach 8: Safe Haven</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+8: Safe Haven</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -6198,7 +6313,10 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 4: Street Outreach 8: Safe Haven</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+8: Safe Haven</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -6268,14 +6386,14 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>10: One night or less
-11: Two to six nights
-2: One week or more, but less than one month
-3: One month or more, but less than 90 days
-4: 90 days or more, but less than one year
-5: One year or longer
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>10: One night or less;
+11: Two to six nights;
+2: One week or more, but less than one month;
+3: One month or more, but less than 90 days;
+4: 90 days or more, but less than one year;
+5: One year or longer;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -6291,7 +6409,10 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 4: Street Outreach 8: Safe Haven</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+8: Safe Haven</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -6372,7 +6493,10 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 4: Street Outreach 8: Safe Haven</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+8: Safe Haven</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -6442,12 +6566,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>1: One Time
-2: Two times
-3: Three times
-4: Four or more times
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: One Time;
+2: Two times;
+3: Three times;
+4: Four or more times;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -6463,7 +6587,10 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 4: Street Outreach 8: Safe Haven</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+8: Safe Haven</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -6533,11 +6660,11 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>101: One month (this time is the first month)
-102-112: ([integers 2-12])
-113: More than 12 months
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>101: One month (this time is the first month);
+102-112: ([integers 2-12]);
+113: More than 12 months;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -6553,7 +6680,10 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 4: Street Outreach 8: Safe Haven</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+8: Safe Haven</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6634,7 +6764,16 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 7: Other 9: PH – Housing Only 10: PH – Housing with Services (no disability required for entry) 11: Day Shelter 12: Homelessness Prevention 13: PH – Rapid Re-Housing 14: Coordinated Entry</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+7: Other;
+9: PH – Housing Only;
+10: PH – Housing with Services (no disability required for entry);
+11: Day Shelter;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing;
+14: Coordinated Entry</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -6719,7 +6858,16 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 7: Other 9: PH – Housing Only 10: PH – Housing with Services (no disability required for entry) 11: Day Shelter 12: Homelessness Prevention 13: PH – Rapid Re-Housing 14: Coordinated Entry</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+7: Other;
+9: PH – Housing Only;
+10: PH – Housing with Services (no disability required for entry);
+11: Day Shelter;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing;
+14: Coordinated Entry</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -6789,14 +6937,14 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>10: One night or less
-11: Two to six nights
-2: One week or more, but less than one month
-3: One month or more, but less than 90 days
-4: 90 days or more, but less than one year
-5: One year or longer
-8: Client doesn't know
-9: Client prefers not to answer
+          <t>10: One night or less;
+11: Two to six nights;
+2: One week or more, but less than one month;
+3: One month or more, but less than 90 days;
+4: 90 days or more, but less than one year;
+5: One year or longer;
+8: Client doesn't know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -6812,7 +6960,16 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 7: Other 9: PH – Housing Only 10: PH – Housing with Services (no disability required for entry) 11: Day Shelter 12: Homelessness Prevention 13: PH – Rapid Re-Housing 14: Coordinated Entry</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+7: Other;
+9: PH – Housing Only;
+10: PH – Housing with Services (no disability required for entry);
+11: Day Shelter;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing;
+14: Coordinated Entry</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -6882,7 +7039,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -6898,7 +7055,16 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 7: Other 9: PH – Housing Only 10: PH – Housing with Services (no disability required for entry) 11: Day Shelter 12: Homelessness Prevention 13: PH – Rapid Re-Housing 14: Coordinated Entry</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+7: Other;
+9: PH – Housing Only;
+10: PH – Housing with Services (no disability required for entry);
+11: Day Shelter;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing;
+14: Coordinated Entry</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -6938,7 +7104,8 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>[If No – no other response options required] [If Yes – use Field #2 response options 10, 11, 2, 3 and go to Field 2C]</t>
+          <t>[If No – no other response options required];
+[If Yes – use Field #2 response options 10, 11, 2, 3 and go to Field 2C]</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -6976,7 +7143,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -6992,7 +7159,16 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 7: Other 9: PH – Housing Only 10: PH – Housing with Services (no disability required for entry) 11: Day Shelter 12: Homelessness Prevention 13: PH – Rapid Re-Housing 14: Coordinated Entry</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+7: Other;
+9: PH – Housing Only;
+10: PH – Housing with Services (no disability required for entry);
+11: Day Shelter;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing;
+14: Coordinated Entry</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -7032,7 +7208,8 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>[If No – no other response options required] [If Yes – use Field #2 response options 10, 11, and go to Field 2C]</t>
+          <t>[If No – no other response options required];
+[If Yes – use Field #2 response options 10, 11, and go to Field 2C]</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -7070,7 +7247,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -7086,7 +7263,16 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 7: Other 9: PH – Housing Only 10: PH – Housing with Services (no disability required for entry) 11: Day Shelter 12: Homelessness Prevention 13: PH – Rapid Re-Housing 14: Coordinated Entry</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+7: Other;
+9: PH – Housing Only;
+10: PH – Housing with Services (no disability required for entry);
+11: Day Shelter;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing;
+14: Coordinated Entry</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -7126,7 +7312,8 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>[If No – no other response options required] [If Yes – go to Field 3, followed by Field 4, and then Field 5]</t>
+          <t>[If No – no other response options required];
+[If Yes – go to Field 3, followed by Field 4, and then Field 5]</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -7175,7 +7362,16 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 7: Other 9: PH – Housing Only 10: PH – Housing with Services (no disability required for entry) 11: Day Shelter 12: Homelessness Prevention 13: PH – Rapid Re-Housing 14: Coordinated Entry</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+7: Other;
+9: PH – Housing Only;
+10: PH – Housing with Services (no disability required for entry);
+11: Day Shelter;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing;
+14: Coordinated Entry</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -7249,12 +7445,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>1: One Time
-2: Two times
-3: Three times
-4: Four or more times
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: One Time;
+2: Two times;
+3: Three times;
+4: Four or more times;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -7270,7 +7466,16 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 7: Other 9: PH – Housing Only 10: PH – Housing with Services (no disability required for entry) 11: Day Shelter 12: Homelessness Prevention 13: PH – Rapid Re-Housing 14: Coordinated Entry</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+7: Other;
+9: PH – Housing Only;
+10: PH – Housing with Services (no disability required for entry);
+11: Day Shelter;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing;
+14: Coordinated Entry</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -7344,11 +7549,11 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>101: One month (this time is the first month)
-102-112: ([integers 2-12])
-113: More than 12 months
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>101: One month (this time is the first month);
+102-112: ([integers 2-12]);
+113: More than 12 months;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -7364,7 +7569,16 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 7: Other 9: PH – Housing Only 10: PH – Housing with Services (no disability required for entry) 11: Day Shelter 12: Homelessness Prevention 13: PH – Rapid Re-Housing 14: Coordinated Entry</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+7: Other;
+9: PH – Housing Only;
+10: PH – Housing with Services (no disability required for entry);
+11: Day Shelter;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing;
+14: Coordinated Entry</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -7444,7 +7658,22 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -7519,11 +7748,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
-99: Data not collected [If yes for “Income from any source”] Indicate all sources and dollar amounts for the source that apply</t>
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
+99: Data not collected;
+[If yes for “Income from any source”] Indicate all sources and dollar amounts for the source that apply</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -7533,7 +7763,22 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -7608,7 +7853,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -7619,7 +7864,22 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -7700,7 +7960,22 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -7775,7 +8050,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -7786,7 +8061,22 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -7867,7 +8157,22 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -7942,7 +8247,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -7953,7 +8258,22 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -8034,7 +8354,22 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -8109,7 +8444,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -8120,7 +8455,22 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -8201,7 +8551,22 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -8276,7 +8641,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -8287,7 +8652,22 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -8368,7 +8748,22 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -8443,7 +8838,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -8454,7 +8849,22 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -8535,7 +8945,22 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -8610,7 +9035,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -8621,7 +9046,22 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -8702,7 +9142,22 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -8777,7 +9232,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -8788,7 +9243,22 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -8869,7 +9339,22 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -8944,7 +9429,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -8955,7 +9440,22 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -9036,7 +9536,22 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -9111,7 +9626,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -9122,7 +9637,22 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -9203,7 +9733,22 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -9278,7 +9823,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -9289,7 +9834,22 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -9370,7 +9930,22 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -9445,7 +10020,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -9456,7 +10031,22 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -9537,7 +10127,22 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -9612,7 +10217,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -9623,7 +10228,22 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -9704,7 +10324,22 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -9779,7 +10414,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -9790,7 +10425,22 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -9871,7 +10521,22 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -9946,7 +10611,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -9957,7 +10622,22 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -10038,7 +10718,22 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -10119,7 +10814,22 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -10200,7 +10910,22 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -10281,7 +11006,22 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -10356,11 +11096,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
-99: Data not collected [If yes for Non-cash benefits from any source”] Indicate all sources that apply</t>
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
+99: Data not collected;
+[If yes for Non-cash benefits from any source”] Indicate all sources that apply</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -10370,7 +11111,22 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -10445,7 +11201,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -10456,7 +11212,22 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -10531,7 +11302,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -10542,7 +11313,22 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -10617,7 +11403,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -10628,7 +11414,22 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -10703,7 +11504,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -10714,7 +11515,22 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -10789,7 +11605,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -10800,7 +11616,22 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -10875,7 +11706,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -10886,7 +11717,22 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -10967,7 +11813,22 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for BCP (HP and ES), MGH, TLP, and Demo;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -11048,7 +11909,22 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -11123,11 +11999,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
-99: Data not collected [If yes for “Covered by Health Insurance”] Indicate all sources that apply</t>
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
+99: Data not collected;
+[If yes for “Covered by Health Insurance”] Indicate all sources that apply</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -11137,7 +12014,22 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -11212,7 +12104,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -11223,7 +12115,22 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -11298,7 +12205,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -11309,7 +12216,22 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -11384,7 +12306,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -11395,7 +12317,22 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -11470,7 +12407,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -11481,7 +12418,22 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -11556,7 +12508,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -11567,7 +12519,22 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -11642,7 +12609,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -11653,7 +12620,22 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -11728,7 +12710,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -11739,7 +12721,22 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -11814,7 +12811,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -11825,7 +12822,22 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -11900,7 +12912,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -11911,7 +12923,22 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -11986,7 +13013,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes (text) (if yes to other-Specify source)</t>
         </is>
       </c>
@@ -11997,7 +13024,22 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -12072,12 +13114,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>1: Applied; decision pending
-2: Applied; client not eligible
-3: Client did not apply
-4: Insurance type N/A for this client
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Applied; decision pending;
+2: Applied; client not eligible;
+3: Client did not apply;
+4: Insurance type N/A for this client;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -12088,7 +13130,22 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components except ES-NbN HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components except ES-NbN;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -12169,7 +13226,17 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -12244,10 +13311,10 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -12258,7 +13325,17 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -12333,10 +13410,10 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -12347,7 +13424,17 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -12428,7 +13515,17 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -12503,10 +13600,10 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -12517,7 +13614,17 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -12598,7 +13705,17 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -12673,10 +13790,10 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -12687,7 +13804,17 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -12762,10 +13889,10 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -12776,7 +13903,17 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -12857,7 +13994,15 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -12932,10 +14077,10 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -12946,7 +14091,15 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -13027,7 +14180,17 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -13102,10 +14265,10 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -13116,7 +14279,17 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -13191,10 +14364,10 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -13205,7 +14378,17 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -13286,7 +14469,17 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -13361,12 +14554,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Alcohol use disorder
-2: Drug use disorder
-3: Both alcohol and drug use disorders
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Alcohol use disorder;
+2: Drug use disorder;
+3: Both alcohol and drug use disorders;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -13377,7 +14570,17 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -13452,11 +14655,11 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>3: Expected to be of long–continued and indefinite duration and substantially impairs ability to live independently
-0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>3: Expected to be of long–continued and indefinite duration and substantially impairs ability to live independently;
+0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -13467,7 +14670,17 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components HHS: RHY – Collection required for all components</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection required for all components</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -13548,7 +14761,20 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -13623,10 +14849,10 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -13637,7 +14863,20 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -13712,12 +14951,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>1: Within the past three months
-2: Three to six months ago (excluding six months exactly)
-3: Six months to one year ago (excluding one year exactly)
-4: One year ago, or more
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Within the past three months;
+2: Three to six months ago (excluding six months exactly);
+3: Six months to one year ago (excluding one year exactly);
+4: One year ago, or more;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -13728,7 +14967,20 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -13803,10 +15055,10 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -13817,7 +15069,20 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all permanent housing projects HHS: PATH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components except SSO Coordinated Entry;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter or Street Outreach;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for all components except SSO Coordinated Entry;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all permanent housing projects;
+HHS: PATH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -13898,12 +15163,22 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition HUD: ESG – Collection only required for Street Outreach, and NbN shelter HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HHS: PATH – Collection required for all components HHS: RHY – Collection only required for Street Outreach</t>
+          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition;
+HUD: ESG – Collection only required for Street Outreach, and NbN shelter;
+HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN;
+HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for Street Outreach</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>1: Emergency Shelter – Night-by-Night 4: Street Outreach 6: Services Only 14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
+          <t>1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+6: Services Only;
+14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -13979,12 +15254,22 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition HUD: ESG – Collection only required for Street Outreach, and NbN shelter HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HHS: PATH – Collection required for all components HHS: RHY – Collection only required for Street Outreach</t>
+          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition;
+HUD: ESG – Collection only required for Street Outreach, and NbN shelter;
+HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN;
+HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for Street Outreach</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>1: Emergency Shelter – Night-by-Night 4: Street Outreach 6: Services Only 14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
+          <t>1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+6: Services Only;
+14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -14060,12 +15345,22 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition HUD: ESG – Collection only required for Street Outreach, and NbN shelter HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HHS: PATH – Collection required for all components HHS: RHY – Collection only required for Street Outreach</t>
+          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition;
+HUD: ESG – Collection only required for Street Outreach, and NbN shelter;
+HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN;
+HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for Street Outreach</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>1: Emergency Shelter – Night-by-Night 4: Street Outreach 6: Services Only 14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
+          <t>1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+6: Services Only;
+14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -14135,10 +15430,10 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn't know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn't know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -14149,12 +15444,22 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition HUD: ESG – Collection only required for Street Outreach, and NbN shelter HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HHS: PATH – Collection required for all components HHS: RHY – Collection only required for Street Outreach</t>
+          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition;
+HUD: ESG – Collection only required for Street Outreach, and NbN shelter;
+HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN;
+HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for Street Outreach</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>1: Emergency Shelter – Night-by-Night 4: Street Outreach 6: Services Only 14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
+          <t>1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+6: Services Only;
+14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -14224,10 +15529,10 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn't know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn't know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -14238,12 +15543,22 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition HUD: ESG – Collection only required for Street Outreach, and NbN shelter HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HHS: PATH – Collection required for all components HHS: RHY – Collection only required for Street Outreach</t>
+          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition;
+HUD: ESG – Collection only required for Street Outreach, and NbN shelter;
+HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN;
+HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for Street Outreach</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>1: Emergency Shelter – Night-by-Night 4: Street Outreach 6: Services Only 14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
+          <t>1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+6: Services Only;
+14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -14313,10 +15628,10 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn't know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn't know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -14327,12 +15642,22 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition HUD: ESG – Collection only required for Street Outreach, and NbN shelter HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HHS: PATH – Collection required for all components HHS: RHY – Collection only required for Street Outreach</t>
+          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition;
+HUD: ESG – Collection only required for Street Outreach, and NbN shelter;
+HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN;
+HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for Street Outreach</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>1: Emergency Shelter – Night-by-Night 4: Street Outreach 6: Services Only 14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
+          <t>1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+6: Services Only;
+14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -14402,10 +15727,10 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn't know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn't know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -14416,12 +15741,22 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition HUD: ESG – Collection only required for Street Outreach, and NbN shelter HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HHS: PATH – Collection required for all components HHS: RHY – Collection only required for Street Outreach</t>
+          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition;
+HUD: ESG – Collection only required for Street Outreach, and NbN shelter;
+HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN;
+HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for Street Outreach</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>1: Emergency Shelter – Night-by-Night 4: Street Outreach 6: Services Only 14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
+          <t>1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+6: Services Only;
+14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -14491,10 +15826,10 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn't know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn't know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -14505,12 +15840,22 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition HUD: ESG – Collection only required for Street Outreach, and NbN shelter HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HHS: PATH – Collection required for all components HHS: RHY – Collection only required for Street Outreach</t>
+          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition;
+HUD: ESG – Collection only required for Street Outreach, and NbN shelter;
+HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN;
+HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for Street Outreach</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>1: Emergency Shelter – Night-by-Night 4: Street Outreach 6: Services Only 14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
+          <t>1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+6: Services Only;
+14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -14586,12 +15931,22 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition HUD: ESG – Collection only required for Street Outreach, and NbN shelter HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry HHS: PATH – Collection required for all components HHS: RHY – Collection only required for Street Outreach</t>
+          <t>HUD: CoC – Collection required for SSO - Street Outreach, SSO - Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for any project type serving clients who meet Category 2 or 3 of the homeless definition;
+HUD: ESG – Collection only required for Street Outreach, and NbN shelter;
+HUD: ESG RUSH – Collection required for Street Outreach, Coordinated Entry, and ES - NbN;
+HUD: Unsheltered Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HUD: Rural Special NOFO – Collection required for SSO – Street Outreach, SSO – Coordinated Entry;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for Street Outreach</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>1: Emergency Shelter – Night-by-Night 4: Street Outreach 6: Services Only 14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
+          <t>1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+6: Services Only;
+14: Coordinated Entry (or other depending on CoC design of Coordinated Entry system)</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -14667,12 +16022,20 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection only required for Street Outreach HUD: CoC – Youth Homeless Demonstration Program (YHDP) - Collection required for Street Outreach HUD: ESG – Collection only required for Street Outreach and ES – NbN HUD: Unsheltered Special NOFO – Collection required for Street Outreach HUD: Rural Special NOFO – Collection required for Street Outreach HHS: PATH – Collection required for all components HHS: RHY – Collection only required for Street Outreach</t>
+          <t>HUD: CoC – Collection only required for Street Outreach;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) - Collection required for Street Outreach;
+HUD: ESG – Collection only required for Street Outreach and ES – NbN;
+HUD: Unsheltered Special NOFO – Collection required for Street Outreach;
+HUD: Rural Special NOFO – Collection required for Street Outreach;
+HHS: PATH – Collection required for all components;
+HHS: RHY – Collection only required for Street Outreach</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>1: Emergency Shelter – Night-by-Night 4: Street Outreach 6: Services Only</t>
+          <t>1: Emergency Shelter – Night-by-Night;
+4: Street Outreach;
+6: Services Only</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -14748,7 +16111,8 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>HUD: ESG – Collection required for ES – NbN HUD: ESG RUSH – Collection required for ES - NbN</t>
+          <t>HUD: ESG – Collection required for ES – NbN;
+HUD: ESG RUSH – Collection required for ES - NbN</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -14829,7 +16193,9 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -14910,7 +16276,9 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
@@ -14985,8 +16353,8 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>1: Phone
-2: Virtual
+          <t>1: Phone;
+2: Virtual;
 3: In person</t>
         </is>
       </c>
@@ -14997,7 +16365,9 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -15072,7 +16442,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>1: Crisis Needs Assessment
+          <t>1: Crisis Needs Assessment;
 2: Housing Needs Assessment</t>
         </is>
       </c>
@@ -15083,7 +16453,9 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -15168,7 +16540,9 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -15253,7 +16627,9 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -15338,7 +16714,9 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -15423,7 +16801,9 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -15498,7 +16878,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>1: Placed on prioritization list
+          <t>1: Placed on prioritization list;
 2: Not placed on prioritization list</t>
         </is>
       </c>
@@ -15509,7 +16889,9 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -15590,7 +16972,9 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -15665,24 +17049,24 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>[Access Events]
-1: Referral to Prevention Assistance project
-2: Problem Solving/Diversion/Rapid Resolution intervention or service
-3: Referral to scheduled Coordinated Entry Crisis Needs Assessment
-4: Referral to scheduled Coordinated Entry Housing Needs Assessment
-[Referral Events]
-5: Referral to post-placement/follow-up case management
-6: Referral to Street Outreach project or services
-7: Referral to Housing Navigation project or services
-8: Referral to Non-continuum services: Ineligible for continuum services
-9: Referral to Non-continuum services: No availability in continuum services
-10: Referral to Emergency Shelter bed opening
-11: Referral to Transitional Housing bed/unit opening
-12: Referral to Joint TH-RRH project/unit/resource opening
-13: Referral to RRH project resource opening
-14: Referral to PSH project resource opening
-15: Referral to Other PH project/unit/resource opening
-16: Referral to emergency assistance/flex fund/furniture assistance
+          <t>[Access Events];
+1: Referral to Prevention Assistance project;
+2: Problem Solving/Diversion/Rapid Resolution intervention or service;
+3: Referral to scheduled Coordinated Entry Crisis Needs Assessment;
+4: Referral to scheduled Coordinated Entry Housing Needs Assessment;
+[Referral Events];
+5: Referral to post-placement/follow-up case management;
+6: Referral to Street Outreach project or services;
+7: Referral to Housing Navigation project or services;
+8: Referral to Non-continuum services: Ineligible for continuum services;
+9: Referral to Non-continuum services: No availability in continuum services;
+10: Referral to Emergency Shelter bed opening;
+11: Referral to Transitional Housing bed/unit opening;
+12: Referral to Joint TH-RRH project/unit/resource opening;
+13: Referral to RRH project resource opening;
+14: Referral to PSH project resource opening;
+15: Referral to Other PH project/unit/resource opening;
+16: Referral to emergency assistance/flex fund/furniture assistance;
 18: Referral to a Housing Stability Voucher</t>
         </is>
       </c>
@@ -15693,7 +17077,9 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -15768,7 +17154,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -15779,7 +17165,9 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -15854,7 +17242,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -15865,7 +17253,9 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -15946,7 +17336,9 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -16021,8 +17413,8 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>1: Successful referral: client accepted
-2: Unsuccessful referral: client rejected
+          <t>1: Successful referral: client accepted;
+2: Unsuccessful referral: client rejected;
 3: Unsuccessful referral: provider rejected</t>
         </is>
       </c>
@@ -16033,7 +17425,9 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -16114,7 +17508,9 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components providing Coordinated Entry HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry HUD: ESG – Collection required for all components providing Coordinated Entry</t>
+          <t>HUD: CoC – Collection required for all components providing Coordinated Entry;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components providing Coordinated Entry;
+HUD: ESG – Collection required for all components providing Coordinated Entry</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -16189,10 +17585,10 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>0: Female
-1: Male
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: Female;
+1: Male;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -16203,12 +17599,36 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for all components HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components HUD: CoC Builds – Collection required for all components HUD: ESG – Collection required for all components HUD: ESG RUSH – Collection required for all components except Emergency Shelter HUD: HOPWA – Collection required for all components HUD: Unsheltered Special NOFO – Collection required for all components HUD: Rural Special NOFO – Collection required for all components HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management HUD: PFS – Collection required for all components HHS: PATH – Street Outreach &amp; Supportive Services Only HHS: RHY – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: CoC – Collection required for all components;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for all components;
+HUD: CoC Builds – Collection required for all components;
+HUD: ESG – Collection required for all components;
+HUD: ESG RUSH – Collection required for all components except Emergency Shelter;
+HUD: HOPWA – Collection required for all components;
+HUD: Unsheltered Special NOFO – Collection required for all components;
+HUD: Rural Special NOFO – Collection required for all components;
+HUD: HUD-VASH – Collection required for HUD VASH Collaborative Case Management;
+HUD: PFS – Collection required for all components;
+HHS: PATH – Street Outreach &amp; Supportive Services Only;
+HHS: RHY – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 1: Emergency Shelter – Night-by-Night 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 4: Street Outreach 6: Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+1: Emergency Shelter – Night-by-Night;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+4: Street Outreach;
+6: Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -16284,7 +17704,11 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for Permanent Supportive Housing HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for Permanent Supportive Housing HUD: CoC Builds – Collection required for Permanent Supportive Housing HUD: Unsheltered Special NOFO – Collection required for Permanent Supportive Housing HUD: Rural Special NOFO – Collection required for Permanent Supportive Housing</t>
+          <t>HUD: CoC – Collection required for Permanent Supportive Housing;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for Permanent Supportive Housing;
+HUD: CoC Builds – Collection required for Permanent Supportive Housing;
+HUD: Unsheltered Special NOFO – Collection required for Permanent Supportive Housing;
+HUD: Rural Special NOFO – Collection required for Permanent Supportive Housing</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -16359,10 +17783,10 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>1: Subsidized housing application assistance
-2: Financial assistance for Moving On (e.g., security deposit, moving expenses)
-3: Non-financial assistance for Moving On (e.g., housing navigation, transition support)
-4: Housing referral/placement
+          <t>1: Subsidized housing application assistance;
+2: Financial assistance for Moving On (e.g., security deposit, moving expenses);
+3: Non-financial assistance for Moving On (e.g., housing navigation, transition support);
+4: Housing referral/placement;
 5: Other (please specify)</t>
         </is>
       </c>
@@ -16373,7 +17797,11 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for Permanent Supportive Housing HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for Permanent Supportive Housing HUD: CoC Builds – Collection required for Permanent Supportive Housing HUD: Unsheltered Special NOFO – Collection required for Permanent Supportive Housing HUD: Rural Special NOFO – Collection required for Permanent Supportive Housing</t>
+          <t>HUD: CoC – Collection required for Permanent Supportive Housing;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for Permanent Supportive Housing;
+HUD: CoC Builds – Collection required for Permanent Supportive Housing;
+HUD: Unsheltered Special NOFO – Collection required for Permanent Supportive Housing;
+HUD: Rural Special NOFO – Collection required for Permanent Supportive Housing</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
@@ -16454,7 +17882,11 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required for Permanent Supportive Housing HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for Permanent Supportive Housing HUD: CoC Builds – Collection required for Permanent Supportive Housing HUD: Unsheltered Special NOFO – Collection required for Permanent Supportive Housing HUD: Rural Special NOFO – Collection required for Permanent Supportive Housing</t>
+          <t>HUD: CoC – Collection required for Permanent Supportive Housing;
+HUD: CoC – Youth Homeless Demonstration Program (YHDP) – Collection required for Permanent Supportive Housing;
+HUD: CoC Builds – Collection required for Permanent Supportive Housing;
+HUD: Unsheltered Special NOFO – Collection required for Permanent Supportive Housing;
+HUD: Rural Special NOFO – Collection required for Permanent Supportive Housing</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -16540,7 +17972,10 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 13: PH – Rapid Re-Housing</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -16610,11 +18045,11 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>0: Not currently enrolled in any school or educational course
-1: Currently enrolled but NOT attending regularly (when school or the course is in session)
-2: Currently enrolled and attending regularly (when school or the course is in session)
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: Not currently enrolled in any school or educational course;
+1: Currently enrolled but NOT attending regularly (when school or the course is in session);
+2: Currently enrolled and attending regularly (when school or the course is in session);
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -16630,7 +18065,10 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 13: PH – Rapid Re-Housing</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -16700,16 +18138,16 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>0: K12: Graduated from high school
-1: K12: Obtained GED
-2: K12: Dropped out
-3: K12: Suspended
-4: K12: Expelled
-5: Higher education: Pursuing a credential but not currently attending
-6: Higher education: Dropped out
-7: Higher education: Obtained a credential/degree
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: K12: Graduated from high school;
+1: K12: Obtained GED;
+2: K12: Dropped out;
+3: K12: Suspended;
+4: K12: Expelled;
+5: Higher education: Pursuing a credential but not currently attending;
+6: Higher education: Dropped out;
+7: Higher education: Obtained a credential/degree;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -16725,7 +18163,10 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 13: PH – Rapid Re-Housing</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -16795,13 +18236,13 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>0: Pursuing a high school diploma or GED
-1: Pursuing Associate’s Degree
-2: Pursuing Bachelor’s Degree
-3: Pursuing Graduate Degree
-4: Pursuing other post-secondary credential
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: Pursuing a high school diploma or GED;
+1: Pursuing Associate’s Degree;
+2: Pursuing Bachelor’s Degree;
+3: Pursuing Graduate Degree;
+4: Pursuing other post-secondary credential;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -16817,7 +18258,10 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 13: PH – Rapid Re-Housing</t>
+          <t>2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -16898,7 +18342,11 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter - Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter - Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -16968,19 +18416,19 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>1: Adult day care and personal assistance
-2: Case management
-3: Child care
-4: Criminal justice/legal services
-5: Education
-6: Employment and training services
-7: Food/meals/nutritional services
-8: Health/medical care
-9: Life skills training
-10: Mental health care/counseling
-11: Outreach and/or engagement
-12: Substance use services/treatment
-13: Transportation
+          <t>1: Adult day care and personal assistance;
+2: Case management;
+3: Child care;
+4: Criminal justice/legal services;
+5: Education;
+6: Employment and training services;
+7: Food/meals/nutritional services;
+8: Health/medical care;
+9: Life skills training;
+10: Mental health care/counseling;
+11: Outreach and/or engagement;
+12: Substance use services/treatment;
+13: Transportation;
 14: Other HOPWA funded service</t>
         </is>
       </c>
@@ -16996,7 +18444,11 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter - Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter - Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -17077,7 +18529,8 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>6: Services Only 12: Homelessness Prevention</t>
+          <t>6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -17147,10 +18600,10 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>1: Rental assistance [collect for PHP and STRMU and PH-TBRA]
-2: Security deposits [collect for PHP]
-3: Utility deposits [collect for PHP]
-4: Utility payments [collect for PHP and STRMU]
+          <t>1: Rental assistance [collect for PHP and STRMU and PH-TBRA];
+2: Security deposits [collect for PHP];
+3: Utility deposits [collect for PHP];
+4: Utility payments [collect for PHP and STRMU];
 7: Mortgage assistance [collect for STRMU]</t>
         </is>
       </c>
@@ -17166,7 +18619,8 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>6: Services Only 12: Homelessness Prevention</t>
+          <t>6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -17247,7 +18701,8 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>6: Services Only 12: Homelessness Prevention</t>
+          <t>6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -17328,7 +18783,11 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -17398,10 +18857,10 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -17417,7 +18876,11 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -17487,12 +18950,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>1: Applied; decision pending
-2: Applied; client not eligible
-3: Client did not apply
-4: Insurance type N/A for this client
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Applied; decision pending;
+2: Applied; client not eligible;
+3: Client did not apply;
+4: Insurance type N/A for this client;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -17508,7 +18971,11 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -17578,10 +19045,10 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -17597,7 +19064,11 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -17667,12 +19138,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>1: Applied; decision pending
-2: Applied; client not eligible
-3: Client did not apply
-4: Insurance type N/A for this client
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Applied; decision pending;
+2: Applied; client not eligible;
+3: Client did not apply;
+4: Insurance type N/A for this client;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -17688,7 +19159,11 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -17769,7 +19244,11 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -17839,10 +19318,10 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -17858,7 +19337,11 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -17939,7 +19422,11 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -18009,8 +19496,8 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>1: Medical Report
-2: Client report
+          <t>1: Medical Report;
+2: Client report;
 3: Other</t>
         </is>
       </c>
@@ -18026,7 +19513,11 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -18096,11 +19587,11 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>0: Not Available
-1: Available
-2: Undetectable
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: Not Available;
+1: Available;
+2: Undetectable;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -18116,7 +19607,11 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -18197,7 +19692,11 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -18267,8 +19766,8 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>1: Medical Report
-2: Client report
+          <t>1: Medical Report;
+2: Client report;
 3: Other</t>
         </is>
       </c>
@@ -18284,7 +19783,11 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -18354,16 +19857,16 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>1: Able to maintain the housing they had at project entry
-2: Moved to new housing unit
-3: Moved in with family/friends on a temporary basis
-4: Moved in with family/friends on a permanent basis
-5: Moved to a transitional or temporary housing facility or program
-6: Client became homeless – moving to a shelter or place unfit for human habitation
-7: Jail/prison
-10: Deceased
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Able to maintain the housing they had at project entry;
+2: Moved to new housing unit;
+3: Moved in with family/friends on a temporary basis;
+4: Moved in with family/friends on a permanent basis;
+5: Moved to a transitional or temporary housing facility or program;
+6: Client became homeless – moving to a shelter or place unfit for human habitation;
+7: Jail/prison;
+10: Deceased;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -18374,12 +19877,19 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required only for Homelessness Prevention component HUD: ESG – Collection required only for Homelessness Prevention component HUD: ESG-RUSH – Collection required for Homelessness Prevention component HUD: HOPWA – Collection required for all components</t>
+          <t>HUD: CoC – Collection required only for Homelessness Prevention component;
+HUD: ESG – Collection required only for Homelessness Prevention component;
+HUD: ESG-RUSH – Collection required for Homelessness Prevention component;
+HUD: HOPWA – Collection required for all components</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -18449,9 +19959,9 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>1: Without a subsidy
-2: With the subsidy they had at project entry
-3: With an on-going subsidy acquired since project entry
+          <t>1: Without a subsidy;
+2: With the subsidy they had at project entry;
+3: With an on-going subsidy acquired since project entry;
 4: Only with financial assistance other than a subsidy</t>
         </is>
       </c>
@@ -18462,12 +19972,19 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required only for Homelessness Prevention component HUD: ESG – Collection required only for Homelessness Prevention component HUD: ESG-RUSH – Collection required for Homelessness Prevention component HUD: HOPWA – Collection required for all components</t>
+          <t>HUD: CoC – Collection required only for Homelessness Prevention component;
+HUD: ESG – Collection required only for Homelessness Prevention component;
+HUD: ESG-RUSH – Collection required for Homelessness Prevention component;
+HUD: HOPWA – Collection required for all components</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -18537,7 +20054,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>1: With on-going subsidy
+          <t>1: With on-going subsidy;
 2: Without an on-going subsidy</t>
         </is>
       </c>
@@ -18548,12 +20065,19 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>HUD: CoC – Collection required only for Homelessness Prevention component HUD: ESG – Collection required only for Homelessness Prevention component HUD: ESG-RUSH – Collection required for Homelessness Prevention component HUD: HOPWA – Collection required for all components</t>
+          <t>HUD: CoC – Collection required only for Homelessness Prevention component;
+HUD: ESG – Collection required only for Homelessness Prevention component;
+HUD: ESG-RUSH – Collection required for Homelessness Prevention component;
+HUD: HOPWA – Collection required for all components</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -18634,7 +20158,11 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homeless Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homeless Prevention</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -18704,10 +20232,10 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -18723,7 +20251,11 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 12: Homeless Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+12: Homeless Prevention</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -18804,7 +20336,8 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>4: Street Outreach 6: Services Only</t>
+          <t>4: Street Outreach;
+6: Services Only</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -18874,18 +20407,18 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>1: Re-engagement
-2: Screening
-14: Clinical assessment
-3: Habilitation/rehabilitation
-4: Community Mental Health
-5: Substance use treatment
-6: Case management
-7: Residential supportive services
-8: Housing minor renovation
-9: Housing moving assistance
-10: Housing eligibility determination
-11: Security deposits
+          <t>1: Re-engagement;
+2: Screening;
+14: Clinical assessment;
+3: Habilitation/rehabilitation;
+4: Community Mental Health;
+5: Substance use treatment;
+6: Case management;
+7: Residential supportive services;
+8: Housing minor renovation;
+9: Housing moving assistance;
+10: Housing eligibility determination;
+11: Security deposits;
 12: One-time rent for eviction prevention</t>
         </is>
       </c>
@@ -18901,7 +20434,8 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>4: Street Outreach 6: Services Only</t>
+          <t>4: Street Outreach;
+6: Services Only</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -18982,7 +20516,8 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>4: Street Outreach 6: Services Only</t>
+          <t>4: Street Outreach;
+6: Services Only</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -19052,16 +20587,16 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>1: Community Mental Health
-2: Substance Use Treatment
-3: Primary Health/ Dental Care
-4: Job Training
-5: Educational Services
-6: Housing Services
-11: Temporary Housing
-7: Permanent Housing
-8: Income Assistance
-9: Employment Assistance
+          <t>1: Community Mental Health;
+2: Substance Use Treatment;
+3: Primary Health/ Dental Care;
+4: Job Training;
+5: Educational Services;
+6: Housing Services;
+11: Temporary Housing;
+7: Permanent Housing;
+8: Income Assistance;
+9: Employment Assistance;
 10: Medical Insurance</t>
         </is>
       </c>
@@ -19077,7 +20612,8 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>4: Street Outreach 6: Services Only</t>
+          <t>4: Street Outreach;
+6: Services Only</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -19147,8 +20683,8 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>1: Attained
-2: Not attained
+          <t>1: Attained;
+2: Not attained;
 3: Unknown</t>
         </is>
       </c>
@@ -19164,7 +20700,8 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>4: Street Outreach 6: Services Only</t>
+          <t>4: Street Outreach;
+6: Services Only</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -19245,7 +20782,8 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>4: Street Outreach 6: Services Only</t>
+          <t>4: Street Outreach;
+6: Services Only</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -19315,7 +20853,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -19331,7 +20869,8 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>4: Street Outreach 6: Services Only</t>
+          <t>4: Street Outreach;
+6: Services Only</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -19401,8 +20940,8 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>1: Client was found ineligible for PATH
-2: Client was not enrolled for other reason(s)
+          <t>1: Client was found ineligible for PATH;
+2: Client was not enrolled for other reason(s);
 3: Unable to locate client</t>
         </is>
       </c>
@@ -19418,7 +20957,8 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>4: Street Outreach 6: Services Only</t>
+          <t>4: Street Outreach;
+6: Services Only</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -19488,10 +21028,10 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -19502,12 +21042,16 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>HHS: PATH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention</t>
+          <t>HHS: PATH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>4: Street Outreach 6: Services Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>4: Street Outreach;
+6: Services Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -19577,20 +21121,20 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>1: Self-Referral
-2: Individual: Parent/Guardian/Relative/Friend/Foster Parent/Other Individual
-7: Outreach Project
-11: Temporary Shelter
-18: Residential Project
-28: Hotline
-30: Child Welfare/CPS
-34: Juvenile Justice
-35: Law Enforcement/ Police
-37: Mental Hospital
-38: School
-39: Other Organization
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Self-Referral;
+2: Individual: Parent/Guardian/Relative/Friend/Foster Parent/Other Individual;
+7: Outreach Project;
+11: Temporary Shelter;
+18: Residential Project;
+28: Hotline;
+30: Child Welfare/CPS;
+34: Juvenile Justice;
+35: Law Enforcement/ Police;
+37: Mental Hospital;
+38: School;
+39: Other Organization;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -19606,7 +21150,9 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -19687,7 +21233,9 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -19768,7 +21316,8 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -19838,7 +21387,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -19854,7 +21403,8 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -19924,9 +21474,9 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>1: Out of age range
-2: Ward of the State – Immediate Reunification
-3: Ward of the Criminal Justice System – Immediate Reunification
+          <t>1: Out of age range;
+2: Ward of the State – Immediate Reunification;
+3: Ward of the Criminal Justice System – Immediate Reunification;
 4: Other</t>
         </is>
       </c>
@@ -19942,7 +21492,8 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -20012,10 +21563,10 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -20031,7 +21582,8 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
@@ -20101,20 +21653,20 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>1: Less than Grade 5
-2: Grades 5-6
-3: Grades 7-8
-4: Grades 9-11
-5: Grade 12/High school diploma
-6: School program does not have grade levels
-7: GED
-10: Some college
-11: Associate’s degree
-12: Bachelor’s degree
-13: Graduate degree
-14: Vocational certification
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Less than Grade 5;
+2: Grades 5-6;
+3: Grades 7-8;
+4: Grades 9-11;
+5: Grade 12/High school diploma;
+6: School program does not have grade levels;
+7: GED;
+10: Some college;
+11: Associate’s degree;
+12: Bachelor’s degree;
+13: Graduate degree;
+14: Vocational certification;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -20125,12 +21677,18 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for HUD/VASH Collaborative Case Management HHS: RHY – Collection required for all components except for Street Outreach VA: SSVF – Collection required for RRH and Homelessness Prevention</t>
+          <t>HUD: HUD-VASH – Collection required for HUD/VASH Collaborative Case Management;
+HHS: RHY – Collection required for all components except for Street Outreach;
+VA: SSVF – Collection required for RRH and Homelessness Prevention</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -20200,15 +21758,15 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>1: Attending school regularly
-2: Attending school irregularly
-3: Graduated from high school
-4: Obtained GED
-5: Dropped out
-6: Suspended
-7: Expelled
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Attending school regularly;
+2: Attending school irregularly;
+3: Graduated from high school;
+4: Obtained GED;
+5: Dropped out;
+6: Suspended;
+7: Expelled;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -20224,7 +21782,9 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -20300,12 +21860,22 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for HUD/VASH Collaborative Case Management HHS: RHY – Collection required for all components except for Street Outreach VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – collection required for all components</t>
+          <t>HUD: HUD-VASH – Collection required for HUD/VASH Collaborative Case Management;
+HHS: RHY – Collection required for all components except for Street Outreach;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – collection required for all components</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -20375,10 +21945,10 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -20389,12 +21959,22 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for HUD/VASH Collaborative Case Management HHS: RHY – Collection required for all components except for Street Outreach VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – collection required for all components</t>
+          <t>HUD: HUD-VASH – Collection required for HUD/VASH Collaborative Case Management;
+HHS: RHY – Collection required for all components except for Street Outreach;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – collection required for all components</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -20464,8 +22044,8 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>1: Full-time
-2: Part-time
+          <t>1: Full-time;
+2: Part-time;
 3: Seasonal / sporadic (including day labor)</t>
         </is>
       </c>
@@ -20476,12 +22056,22 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for HUD/VASH Collaborative Case Management HHS: RHY – Collection required for all components except for Street Outreach VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – collection required for all components</t>
+          <t>HUD: HUD-VASH – Collection required for HUD/VASH Collaborative Case Management;
+HHS: RHY – Collection required for all components except for Street Outreach;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – collection required for all components</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -20551,8 +22141,8 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>1: Looking for work
-2: Unable to work
+          <t>1: Looking for work;
+2: Unable to work;
 3: Not looking for work</t>
         </is>
       </c>
@@ -20563,12 +22153,22 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for HUD/VASH Collaborative Case Management HHS: RHY – Collection required for all components except for Street Outreach VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – collection required for all components</t>
+          <t>HUD: HUD-VASH – Collection required for HUD/VASH Collaborative Case Management;
+HHS: RHY – Collection required for all components except for Street Outreach;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – collection required for all components</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -20638,13 +22238,13 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>1: Excellent
-2: Very good
-3: Good
-4: Fair
-5: Poor
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Excellent;
+2: Very good;
+3: Good;
+4: Fair;
+5: Poor;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -20655,12 +22255,16 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for HUD/VASH Collaborative Case Management HHS: RHY – Collection required for all components except for Street Outreach</t>
+          <t>HUD: HUD-VASH – Collection required for HUD/VASH Collaborative Case Management;
+HHS: RHY – Collection required for all components except for Street Outreach</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -20730,13 +22334,13 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>1: Excellent
-2: Very good
-3: Good
-4: Fair
-5: Poor
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Excellent;
+2: Very good;
+3: Good;
+4: Fair;
+5: Poor;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -20752,7 +22356,9 @@
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
@@ -20822,13 +22428,13 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>1: Excellent
-2: Very good
-3: Good
-4: Fair
-5: Poor
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Excellent;
+2: Very good;
+3: Good;
+4: Fair;
+5: Poor;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -20844,7 +22450,9 @@
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
@@ -20914,10 +22522,10 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -20933,7 +22541,10 @@
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
@@ -21014,7 +22625,10 @@
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -21084,10 +22698,10 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -21103,7 +22717,9 @@
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
@@ -21173,8 +22789,8 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>1: Less than one year
-2: 1 to 2 years
+          <t>1: Less than one year;
+2: 1 to 2 years;
 3: 3 to 5 or more years</t>
         </is>
       </c>
@@ -21190,7 +22806,9 @@
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -21271,7 +22889,9 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -21341,10 +22961,10 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -21360,7 +22980,9 @@
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
@@ -21430,8 +23052,8 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>1: Less than one year
-2: 1 to 2 years
+          <t>1: Less than one year;
+2: 1 to 2 years;
 3: 3 to 5 or more years</t>
         </is>
       </c>
@@ -21447,7 +23069,9 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
@@ -21528,7 +23152,9 @@
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
@@ -21598,10 +23224,10 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -21617,7 +23243,9 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
@@ -21687,10 +23315,10 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -21706,7 +23334,9 @@
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
@@ -21776,10 +23406,10 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -21795,7 +23425,9 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
@@ -21865,10 +23497,10 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -21884,7 +23516,9 @@
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
@@ -21954,10 +23588,10 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -21973,7 +23607,9 @@
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -22043,10 +23679,10 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -22062,7 +23698,9 @@
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
@@ -22139,7 +23777,10 @@
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
@@ -22181,7 +23822,10 @@
       <c r="O260" s="2" t="inlineStr"/>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>BCP-P, BCP-ES, TLP&amp;MGH, DEMO</t>
+          <t>BCP-P;
+BCP-ES;
+TLP&amp;MGH;
+DEMO</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -22213,20 +23857,20 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>2: Community service/service learning (CSL) [TLP&amp;MGH, DEMO]
-7: Criminal justice /legal services [BCP-P, BCP-ES, TLP&amp;MGH, DEMO]
-5: Education [BCP-P, BCP-ES, TLP&amp;MGH, DEMO]
-6: Employment and/or training services [TLP&amp;MGH, DEMO]
-14: Health/medical care [BCP-P, BCP-ES, TLP&amp;MGH, DEMO]
-26: Home-based Services [BCP-P]
-8: Life skills training [BCP-P, BCP-ES, TLP&amp;MGH, DEMO]
-10: Parenting education for youth with children [BCP-P, BCP-ES, TLP&amp;MGH, DEMO]
-27: Post-natal newborn care (wellness exams; immunizations) [TLP&amp;MGH, DEMO]
-12: Post-natal care for client (person who gave birth) [TLP&amp;MGH, DEMO]
-13: Pre-natal care [TLP&amp;MGH, DEMO]
-28: STD Testing [BCP-P, BCP-ES]
-29: Street-based Services [BCP-P]
-17: Substance use disorder treatment [BCP-P, BCP-ES, TLP&amp;MGH, DEMO]
+          <t>2: Community service/service learning (CSL) [TLP&amp;MGH, DEMO];
+7: Criminal justice /legal services [BCP-P, BCP-ES, TLP&amp;MGH, DEMO];
+5: Education [BCP-P, BCP-ES, TLP&amp;MGH, DEMO];
+6: Employment and/or training services [TLP&amp;MGH, DEMO];
+14: Health/medical care [BCP-P, BCP-ES, TLP&amp;MGH, DEMO];
+26: Home-based Services [BCP-P];
+8: Life skills training [BCP-P, BCP-ES, TLP&amp;MGH, DEMO];
+10: Parenting education for youth with children [BCP-P, BCP-ES, TLP&amp;MGH, DEMO];
+27: Post-natal newborn care (wellness exams; immunizations) [TLP&amp;MGH, DEMO];
+12: Post-natal care for client (person who gave birth) [TLP&amp;MGH, DEMO];
+13: Pre-natal care [TLP&amp;MGH, DEMO];
+28: STD Testing [BCP-P, BCP-ES];
+29: Street-based Services [BCP-P];
+17: Substance use disorder treatment [BCP-P, BCP-ES, TLP&amp;MGH, DEMO];
 18: Substance Use disorder Ed/Prevention Services [BCP-P, BCP-ES, TLP&amp;MGH, DEMO]</t>
         </is>
       </c>
@@ -22238,7 +23882,10 @@
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 6: Services Only 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+6: Services Only;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
@@ -22280,7 +23927,10 @@
       <c r="O261" s="2" t="inlineStr"/>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>BCP-P, BCP-ES, TLP&amp;MGH, DEMO</t>
+          <t>BCP-P;
+BCP-ES;
+TLP&amp;MGH;
+DEMO</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -22312,10 +23962,10 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -22331,7 +23981,10 @@
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -22401,10 +24054,10 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -22420,7 +24073,10 @@
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -22501,7 +24157,10 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
@@ -22571,12 +24230,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>1: 1-3
-2: 4-7
-3: 8-11
-4: 12 or more
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: 1-3;
+2: 4-7;
+3: 8-11;
+4: 12 or more;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -22592,7 +24251,10 @@
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -22673,7 +24335,10 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -22743,10 +24408,10 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -22762,7 +24427,10 @@
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -22843,7 +24511,10 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -22913,10 +24584,10 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -22932,7 +24603,10 @@
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -23002,10 +24676,10 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -23021,7 +24695,9 @@
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -23091,10 +24767,10 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -23110,7 +24786,9 @@
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -23180,10 +24858,10 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -23199,7 +24877,9 @@
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -23269,10 +24949,10 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -23288,7 +24968,9 @@
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 4: Street Outreach</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+4: Street Outreach</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -23358,8 +25040,8 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>1: Completed project
-2: Client voluntarily left early
+          <t>1: Completed project;
+2: Client voluntarily left early;
 3: Client was expelled or otherwise involuntarily discharged from project</t>
         </is>
       </c>
@@ -23375,7 +25057,8 @@
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -23445,11 +25128,11 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>1: Criminal activity/destruction of property/violence
-2: Non-compliance with project rules
-3: Non-payment of rent/occupancy charge
-4: Reached maximum time allowed by project
-5: Project terminated
+          <t>1: Criminal activity/destruction of property/violence;
+2: Non-compliance with project rules;
+3: Non-payment of rent/occupancy charge;
+4: Reached maximum time allowed by project;
+5: Project terminated;
 6: Unknown/disappeared</t>
         </is>
       </c>
@@ -23465,7 +25148,8 @@
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
@@ -23535,7 +25219,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -23551,7 +25235,9 @@
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -23621,8 +25307,8 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>1: Individual
-2: Family
+          <t>1: Individual;
+2: Family;
 3: Group – including peer counseling</t>
         </is>
       </c>
@@ -23638,7 +25324,9 @@
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
@@ -23723,7 +25411,9 @@
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
@@ -23808,7 +25498,9 @@
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
@@ -23878,7 +25570,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -23894,7 +25586,9 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -23964,10 +25658,10 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -23983,7 +25677,8 @@
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -24053,8 +25748,8 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
+          <t>0: No;
+1: Yes;
 2: Worker does not know</t>
         </is>
       </c>
@@ -24070,7 +25765,8 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -24140,8 +25836,8 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
+          <t>0: No;
+1: Yes;
 2: Worker does not know</t>
         </is>
       </c>
@@ -24157,7 +25853,8 @@
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
@@ -24227,8 +25924,8 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
+          <t>0: No;
+1: Yes;
 2: Worker does not know</t>
         </is>
       </c>
@@ -24244,7 +25941,8 @@
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
@@ -24314,8 +26012,8 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
+          <t>0: No;
+1: Yes;
 2: Worker does not know</t>
         </is>
       </c>
@@ -24331,7 +26029,8 @@
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
@@ -24412,7 +26111,9 @@
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
@@ -24482,8 +26183,8 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
+          <t>0: No;
+1: Yes;
 9: Client prefers not to answer</t>
         </is>
       </c>
@@ -24499,7 +26200,9 @@
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
@@ -24569,9 +26272,9 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>1: Via email/social media
-2: Via telephone
-3: In person: one-on-one
+          <t>1: Via email/social media;
+2: Via telephone;
+3: In person: one-on-one;
 4: In person: group</t>
         </is>
       </c>
@@ -24587,7 +26290,9 @@
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 12: Homelessness Prevention</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+12: Homelessness Prevention</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
@@ -24663,12 +26368,23 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Supportive Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Supportive Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
@@ -24744,12 +26460,23 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Supportive Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Supportive Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
@@ -24819,10 +26546,10 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -24833,12 +26560,23 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Supportive Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Supportive Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
@@ -24908,10 +26646,10 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -24922,12 +26660,23 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Supportive Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Supportive Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
@@ -24997,10 +26746,10 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -25011,12 +26760,23 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Supportive Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Supportive Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
@@ -25086,10 +26846,10 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -25100,12 +26860,23 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Supportive Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Supportive Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
@@ -25175,10 +26946,10 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -25189,12 +26960,23 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Supportive Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Supportive Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
@@ -25264,10 +27046,10 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -25278,12 +27060,23 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Supportive Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Supportive Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
@@ -25353,10 +27146,10 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -25367,12 +27160,23 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Supportive Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Supportive Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
@@ -25442,10 +27246,10 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Yes
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>0: No;
+1: Yes;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -25456,12 +27260,23 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Supportive Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Supportive Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
@@ -25531,14 +27346,14 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>1: Army
-2: Air Force
-3: Navy
-4: Marines
-6: Coast Guard
-7: Space Force
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Army;
+2: Air Force;
+3: Navy;
+4: Marines;
+6: Coast Guard;
+7: Space Force;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -25549,12 +27364,23 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Supportive Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Supportive Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
@@ -25624,14 +27450,14 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>1: Honorable
-2: General under honorable conditions
-6: Under other than honorable conditions (OTH)
-4: Bad conduct
-5: Dishonorable
-7: Uncharacterized
-8: Client doesn’t know
-9: Client prefers not to answer
+          <t>1: Honorable;
+2: General under honorable conditions;
+6: Under other than honorable conditions (OTH);
+4: Bad conduct;
+5: Dishonorable;
+7: Uncharacterized;
+8: Client doesn’t know;
+9: Client prefers not to answer;
 99: Data not collected</t>
         </is>
       </c>
@@ -25642,12 +27468,23 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: Community Contract Safe Haven VA: CRS Contract Residential Services</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: Community Contract Safe Haven;
+VA: CRS Contract Residential Services</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Supportive Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Supportive Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G300" s="2" t="inlineStr">
@@ -25728,7 +27565,8 @@
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
@@ -25798,15 +27636,15 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>1: Outreach services
-2: Case management services
-3: Assistance obtaining VA benefits
-4: Assistance obtaining/coordinating other public benefits
-5: Direct provision of other public benefits
-6: Other (non-TFA) supportive service approved by VA
-7: Shallow Subsidy
-8: Returning Home
-9: Rapid Resolution
+          <t>1: Outreach services;
+2: Case management services;
+3: Assistance obtaining VA benefits;
+4: Assistance obtaining/coordinating other public benefits;
+5: Direct provision of other public benefits;
+6: Other (non-TFA) supportive service approved by VA;
+7: Shallow Subsidy;
+8: Returning Home;
+9: Rapid Resolution;
 10: Healthcare Navigation</t>
         </is>
       </c>
@@ -25822,7 +27660,8 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
@@ -25892,9 +27731,9 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>1: VA vocational and rehabilitation counseling
-2: Employment and training services
-3: Educational assistance
+          <t>1: VA vocational and rehabilitation counseling;
+2: Employment and training services;
+3: Educational assistance;
 4: Health care services</t>
         </is>
       </c>
@@ -25910,7 +27749,8 @@
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
@@ -25980,18 +27820,18 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>1: Health care services
-2: Daily living services
-3: Personal financial planning services
-4: Transportation services
-5: Income support services
-6: Fiduciary and representative payee services
-7: Legal services – child support
-8: Legal services – eviction prevention
-9: Legal services – outstanding fines and penalties
-10: Legal services – restore/acquire driver’s license
-11: Legal services – other
-12: Child care
+          <t>1: Health care services;
+2: Daily living services;
+3: Personal financial planning services;
+4: Transportation services;
+5: Income support services;
+6: Fiduciary and representative payee services;
+7: Legal services – child support;
+8: Legal services – eviction prevention;
+9: Legal services – outstanding fines and penalties;
+10: Legal services – restore/acquire driver’s license;
+11: Legal services – other;
+12: Child care;
 13: Housing counseling</t>
         </is>
       </c>
@@ -26007,7 +27847,8 @@
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
@@ -26077,16 +27918,16 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>1: Personal financial planning services
-2: Transportation services
-3: Income support services
-4: Fiduciary and representative payee services
-5: Legal services – child support
-6: Legal services – eviction prevention
-7: Legal services – outstanding fines and penalties
-8: Legal services – restore/acquire driver’s license
-9: Legal services – other
-10: Child care
+          <t>1: Personal financial planning services;
+2: Transportation services;
+3: Income support services;
+4: Fiduciary and representative payee services;
+5: Legal services – child support;
+6: Legal services – eviction prevention;
+7: Legal services – outstanding fines and penalties;
+8: Legal services – restore/acquire driver’s license;
+9: Legal services – other;
+10: Child care;
 11: Housing counseling</t>
         </is>
       </c>
@@ -26102,7 +27943,8 @@
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
@@ -26183,7 +28025,8 @@
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
@@ -26264,7 +28107,8 @@
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
@@ -26345,7 +28189,8 @@
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
@@ -26426,7 +28271,8 @@
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
@@ -26496,19 +28342,19 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>1: Rental assistance
-4: Utility fee payment assistance
-2: Security deposit
-3: Utility deposit
-5: Moving costs
-8: Transportation services: tokens/vouchers
-9: Transportation services: vehicle repair/maintenance
-10: Child care
-12: General housing stability assistance
-14: Emergency housing assistance
-15: Shallow subsidy financial assistance
-16: Food assistance
-17: Landlord incentive
+          <t>1: Rental assistance;
+4: Utility fee payment assistance;
+2: Security deposit;
+3: Utility deposit;
+5: Moving costs;
+8: Transportation services: tokens/vouchers;
+9: Transportation services: vehicle repair/maintenance;
+10: Child care;
+12: General housing stability assistance;
+14: Emergency housing assistance;
+15: Shallow subsidy financial assistance;
+16: Food assistance;
+17: Landlord incentive;
 18: Tenant incentive</t>
         </is>
       </c>
@@ -26524,7 +28370,8 @@
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
@@ -26605,7 +28452,8 @@
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
@@ -26675,9 +28523,9 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>1: 30% or less
-2: 31% to 50%
-3: 51% to 80%
+          <t>1: 30% or less;
+2: 31% to 50%;
+3: 51% to 80%;
 4: 81% or greater</t>
         </is>
       </c>
@@ -26693,7 +28541,8 @@
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr">
@@ -26769,12 +28618,23 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>HUD: HUD-VASH – Collection required for all components VA: SSVF – Collection required for RRH and Homelessness Prevention VA: GPD – Collection required for all components VA: CRS Contract Residential Services VA: Community Contract Safe Haven Program</t>
+          <t>HUD: HUD-VASH – Collection required for all components;
+VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: GPD – Collection required for all components;
+VA: CRS Contract Residential Services;
+VA: Community Contract Safe Haven Program</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>0: Emergency Shelter – Entry Exit 2: Transitional Housing 3: PH – Permanent Supportive Housing (disability required for entry) 6: Services Only 8: Safe Haven 9: PH – Housing Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>0: Emergency Shelter – Entry Exit;
+2: Transitional Housing;
+3: PH – Permanent Supportive Housing (disability required for entry);
+6: Services Only;
+8: Safe Haven;
+9: PH – Housing Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr">
@@ -26844,7 +28704,7 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -26930,9 +28790,9 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>0: 1-6 days
-1: 7-13 days
-2: 14-21 days
+          <t>0: 1-6 days;
+1: 7-13 days;
+2: 14-21 days;
 3: More than 21 days</t>
         </is>
       </c>
@@ -27018,9 +28878,9 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>0: $0 (i.e., not employed, not receiving cash benefits, no other current income)
-1: 1-14% of Area Median Income (AMI) for household size
-2: 15-30% of AMI for household size
+          <t>0: $0 (i.e., not employed, not receiving cash benefits, no other current income);
+1: 1-14% of Area Median Income (AMI) for household size;
+2: 15-30% of AMI for household size;
 3: More than 30% of AMI for household size</t>
         </is>
       </c>
@@ -27106,8 +28966,8 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>0: Most recent episode occurred within the last year
-1: Most recent episode occurred more than one year ago
+          <t>0: Most recent episode occurred within the last year;
+1: Most recent episode occurred more than one year ago;
 2: None</t>
         </is>
       </c>
@@ -27193,7 +29053,7 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -27279,7 +29139,7 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -27365,7 +29225,7 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -27451,8 +29311,8 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>0: No prior rental evictions
-1: 1 prior rental eviction
+          <t>0: No prior rental evictions;
+1: 1 prior rental eviction;
 2: 2 or more prior rental evictions</t>
         </is>
       </c>
@@ -27619,7 +29479,7 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -27705,8 +29565,8 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>0: Not incarcerated
-1: Incarcerated once
+          <t>0: Not incarcerated;
+1: Incarcerated once;
 2: Incarcerated two or more times</t>
         </is>
       </c>
@@ -27792,7 +29652,7 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -27878,7 +29738,7 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -27964,7 +29824,7 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -28050,7 +29910,7 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -28136,7 +29996,7 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -28303,8 +30163,8 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>0: No
-1: Youngest child is under 1 year old
+          <t>0: No;
+1: Youngest child is under 1 year old;
 2: Youngest child is 1 to 6 years old and/or one or more children (any age) require significant care.</t>
         </is>
       </c>
@@ -28390,7 +30250,7 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -28557,7 +30417,7 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>0: No
+          <t>0: No;
 1: Yes</t>
         </is>
       </c>
@@ -28886,17 +30746,17 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>1: Referral package forwarded to PHA
-2: Voucher denied by PHA
-3: Voucher issued by PHA
-4: Voucher revoked or expired
-5: Voucher in use – veteran moved into housing
-6: Voucher was ported locally
-7: Voucher was administratively absorbed by new PHA
-8: Voucher was converted to Housing Choice Voucher
-9: Veteran exited – voucher was returned
-10: Veteran exited – family maintained the voucher
-11: Veteran exited – prior to ever receiving a voucher
+          <t>1: Referral package forwarded to PHA;
+2: Voucher denied by PHA;
+3: Voucher issued by PHA;
+4: Voucher revoked or expired;
+5: Voucher in use – veteran moved into housing;
+6: Voucher was ported locally;
+7: Voucher was administratively absorbed by new PHA;
+8: Voucher was converted to Housing Choice Voucher;
+9: Veteran exited – voucher was returned;
+10: Veteran exited – family maintained the voucher;
+11: Veteran exited – prior to ever receiving a voucher;
 12: Other</t>
         </is>
       </c>
@@ -29063,18 +30923,18 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>1: Accomplished goals and/or obtained services and no longer needs CM
-2: Transferred to another HUD-VASH program site
-3: Found/chose other housing
-4: Did not comply with HUD-VASH CM
-5: Eviction and/or other housing related issues
-6: Unhappy with HUD-VASH housing
-7: No longer financially eligible for HUD-VASH voucher
-8: No longer interested in participating in this program
-9: Veteran cannot be located
-10: Veteran too ill to participate at this time
-11: Veteran is incarcerated
-12: Veteran is deceased
+          <t>1: Accomplished goals and/or obtained services and no longer needs CM;
+2: Transferred to another HUD-VASH program site;
+3: Found/chose other housing;
+4: Did not comply with HUD-VASH CM;
+5: Eviction and/or other housing related issues;
+6: Unhappy with HUD-VASH housing;
+7: No longer financially eligible for HUD-VASH voucher;
+8: No longer interested in participating in this program;
+9: Veteran cannot be located;
+10: Veteran too ill to participate at this time;
+11: Veteran is incarcerated;
+12: Veteran is deceased;
 13: Other</t>
         </is>
       </c>
@@ -29241,9 +31101,9 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>1: Mental health consultation completed
-2: Mental health consultation being coordinated/arranged with VA provider
-3: Mental health consultation being coordinated/arranged with other provider
+          <t>1: Mental health consultation completed;
+2: Mental health consultation being coordinated/arranged with VA provider;
+3: Mental health consultation being coordinated/arranged with other provider;
 4: Offer declined</t>
         </is>
       </c>
@@ -29254,12 +31114,15 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>VA: SSVF – Collection required for RRH and Homelessness Prevention VA: Grant Per Diem – Case Management/Housing Retention</t>
+          <t>VA: SSVF – Collection required for RRH and Homelessness Prevention;
+VA: Grant Per Diem – Case Management/Housing Retention</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
-          <t>6: Services Only 12: Homelessness Prevention 13: PH – Rapid Re-Housing</t>
+          <t>6: Services Only;
+12: Homelessness Prevention;
+13: PH – Rapid Re-Housing</t>
         </is>
       </c>
       <c r="G342" s="2" t="inlineStr">
@@ -29475,10 +31338,10 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>1: Project start
-2: Project update
-5: Project annual assessment
-3: Project exit
+          <t>1: Project start;
+2: Project update;
+5: Project annual assessment;
+3: Project exit;
 6: Post exit</t>
         </is>
       </c>
